--- a/wiki/reports/daily/2026-10-22_일일보고.xlsx
+++ b/wiki/reports/daily/2026-10-22_일일보고.xlsx
@@ -22,7 +22,7 @@
     <numFmt numFmtId="165" formatCode="+0.0%;-0.0%;&quot;-&quot;"/>
     <numFmt numFmtId="166" formatCode="#,##0.0"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -75,13 +75,8 @@
       <color rgb="00FFFFFF"/>
       <sz val="11"/>
     </font>
-    <font>
-      <name val="맑은 고딕"/>
-      <color rgb="00888888"/>
-      <sz val="10"/>
-    </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill/>
     </fill>
@@ -101,6 +96,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FADBD8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D5F5E3"/>
       </patternFill>
     </fill>
     <fill>
@@ -155,7 +155,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -187,25 +187,28 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="164" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="7" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="7" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -213,6 +216,30 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -596,14 +623,14 @@
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>재연마 일일생산 보고  ─  2026년 10월 22일  (2026-10-22 07:59 생성 · 속보값)</t>
+          <t>재연마 일일생산 보고  ─  2026년 10월 22일  (2026-10-22 16:00 생성 · 속보값)</t>
         </is>
       </c>
     </row>
     <row r="2" ht="15" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>생성: 2026-10-22 07:59   |   전일: 10월 21일   |   월평균 기준: 이전 작업일 13일 평균   |   10월 누적 작업일: 13일</t>
+          <t>생성: 2026-10-22 16:00   |   전일: 10월 21일   |   월평균 기준: 이전 작업일 13일 평균   |   10월 누적 작업일: 14일</t>
         </is>
       </c>
     </row>
@@ -665,25 +692,25 @@
         </is>
       </c>
       <c r="B4" s="5" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="C4" s="6" t="n">
         <v>33</v>
       </c>
       <c r="D4" s="7" t="n">
-        <v>-33</v>
+        <v>-6</v>
       </c>
       <c r="E4" s="8" t="n">
-        <v>-1</v>
+        <v>-0.1818181818181818</v>
       </c>
       <c r="F4" s="9" t="n">
         <v>42.6</v>
       </c>
       <c r="G4" s="7" t="n">
-        <v>-42.61538461538461</v>
+        <v>-15.61538461538461</v>
       </c>
       <c r="H4" s="8" t="n">
-        <v>-1</v>
+        <v>-0.3664259927797834</v>
       </c>
       <c r="I4" s="10" t="inlineStr"/>
     </row>
@@ -694,205 +721,205 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>0</v>
+        <v>9585</v>
       </c>
       <c r="C5" s="6" t="n">
         <v>7836</v>
       </c>
-      <c r="D5" s="7" t="n">
-        <v>-7836</v>
-      </c>
-      <c r="E5" s="8" t="n">
-        <v>-1</v>
+      <c r="D5" s="11" t="n">
+        <v>1749</v>
+      </c>
+      <c r="E5" s="12" t="n">
+        <v>0.2232006125574273</v>
       </c>
       <c r="F5" s="9" t="n">
         <v>9676.5</v>
       </c>
       <c r="G5" s="7" t="n">
-        <v>-9676.538461538461</v>
+        <v>-91.53846153846098</v>
       </c>
       <c r="H5" s="8" t="n">
-        <v>-1</v>
+        <v>-0.009459835446559822</v>
       </c>
       <c r="I5" s="10" t="inlineStr">
         <is>
-          <t>0:00:00</t>
+          <t>2:39:45</t>
         </is>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="11" t="inlineStr">
+      <c r="A6" s="13" t="inlineStr">
         <is>
           <t>GX7  수량 (개)</t>
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="C6" s="6" t="n">
         <v>14</v>
       </c>
-      <c r="D6" s="7" t="n">
-        <v>-14</v>
-      </c>
-      <c r="E6" s="8" t="n">
-        <v>-1</v>
+      <c r="D6" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F6" s="9" t="n">
         <v>27.2</v>
       </c>
       <c r="G6" s="7" t="n">
-        <v>-27.23076923076923</v>
+        <v>-13.23076923076923</v>
       </c>
       <c r="H6" s="8" t="n">
-        <v>-1</v>
+        <v>-0.4858757062146892</v>
       </c>
       <c r="I6" s="10" t="inlineStr"/>
     </row>
     <row r="7" ht="22" customHeight="1">
-      <c r="A7" s="11" t="inlineStr">
+      <c r="A7" s="13" t="inlineStr">
         <is>
           <t>GX7  가공시간 (초)</t>
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>0</v>
+        <v>6188</v>
       </c>
       <c r="C7" s="6" t="n">
         <v>7570</v>
       </c>
       <c r="D7" s="7" t="n">
-        <v>-7570</v>
+        <v>-1382</v>
       </c>
       <c r="E7" s="8" t="n">
-        <v>-1</v>
+        <v>-0.1825627476882431</v>
       </c>
       <c r="F7" s="9" t="n">
         <v>9024</v>
       </c>
       <c r="G7" s="7" t="n">
-        <v>-9024</v>
+        <v>-2836</v>
       </c>
       <c r="H7" s="8" t="n">
-        <v>-1</v>
+        <v>-0.31427304964539</v>
       </c>
       <c r="I7" s="10" t="inlineStr">
         <is>
-          <t>0:00:00</t>
+          <t>1:43:08</t>
         </is>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="12" t="inlineStr">
+      <c r="A8" s="16" t="inlineStr">
         <is>
           <t>합계  수량 (개)</t>
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="C8" s="6" t="n">
         <v>47</v>
       </c>
       <c r="D8" s="7" t="n">
-        <v>-47</v>
+        <v>-6</v>
       </c>
       <c r="E8" s="8" t="n">
-        <v>-1</v>
+        <v>-0.1276595744680851</v>
       </c>
       <c r="F8" s="9" t="n">
         <v>69.8</v>
       </c>
       <c r="G8" s="7" t="n">
-        <v>-69.84615384615384</v>
+        <v>-28.84615384615384</v>
       </c>
       <c r="H8" s="8" t="n">
-        <v>-1</v>
+        <v>-0.4129955947136563</v>
       </c>
       <c r="I8" s="10" t="inlineStr"/>
     </row>
     <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="12" t="inlineStr">
+      <c r="A9" s="16" t="inlineStr">
         <is>
           <t>합계  가공시간 (초)</t>
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>0</v>
+        <v>15773</v>
       </c>
       <c r="C9" s="6" t="n">
         <v>15406</v>
       </c>
-      <c r="D9" s="7" t="n">
-        <v>-15406</v>
-      </c>
-      <c r="E9" s="8" t="n">
-        <v>-1</v>
+      <c r="D9" s="11" t="n">
+        <v>367</v>
+      </c>
+      <c r="E9" s="12" t="n">
+        <v>0.02382188757626899</v>
       </c>
       <c r="F9" s="9" t="n">
         <v>18700.5</v>
       </c>
       <c r="G9" s="7" t="n">
-        <v>-18700.53846153846</v>
+        <v>-2927.538461538461</v>
       </c>
       <c r="H9" s="8" t="n">
-        <v>-1</v>
+        <v>-0.1565483511375649</v>
       </c>
       <c r="I9" s="10" t="inlineStr">
         <is>
-          <t>0:00:00</t>
+          <t>4:22:53</t>
         </is>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="12" t="inlineStr">
+      <c r="A10" s="16" t="inlineStr">
         <is>
           <t>합계  금액</t>
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="C10" s="6" t="n">
         <v>47</v>
       </c>
       <c r="D10" s="7" t="n">
-        <v>-47</v>
+        <v>-6</v>
       </c>
       <c r="E10" s="8" t="n">
-        <v>-1</v>
+        <v>-0.1276595744680851</v>
       </c>
       <c r="F10" s="9" t="n">
         <v>69.8</v>
       </c>
       <c r="G10" s="7" t="n">
-        <v>-69.84615384615384</v>
+        <v>-28.84615384615384</v>
       </c>
       <c r="H10" s="8" t="n">
-        <v>-1</v>
+        <v>-0.4129955947136563</v>
       </c>
       <c r="I10" s="10" t="inlineStr"/>
     </row>
     <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="13" t="inlineStr">
-        <is>
-          <t>10월 누적  (13일 / 22일 중 작업일)</t>
-        </is>
-      </c>
-      <c r="B11" s="13" t="n"/>
-      <c r="C11" s="14" t="n">
-        <v>908</v>
-      </c>
-      <c r="D11" s="14" t="n">
-        <v>243107</v>
-      </c>
-      <c r="E11" s="14" t="n">
-        <v>908</v>
-      </c>
-      <c r="F11" s="13" t="n"/>
-      <c r="G11" s="13" t="n"/>
-      <c r="H11" s="13" t="n"/>
-      <c r="I11" s="13" t="n"/>
+      <c r="A11" s="17" t="inlineStr">
+        <is>
+          <t>10월 누적  (14일 / 22일 중 작업일)</t>
+        </is>
+      </c>
+      <c r="B11" s="17" t="n"/>
+      <c r="C11" s="18" t="n">
+        <v>949</v>
+      </c>
+      <c r="D11" s="18" t="n">
+        <v>258880</v>
+      </c>
+      <c r="E11" s="18" t="n">
+        <v>949</v>
+      </c>
+      <c r="F11" s="17" t="n"/>
+      <c r="G11" s="17" t="n"/>
+      <c r="H11" s="17" t="n"/>
+      <c r="I11" s="17" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -910,7 +937,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K8"/>
+  <dimension ref="A1:K13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -934,154 +961,395 @@
       </c>
     </row>
     <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="15" t="inlineStr">
+      <c r="A2" s="19" t="inlineStr">
         <is>
           <t>■ FAST GRIND</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="16" t="inlineStr">
+      <c r="A3" s="20" t="inlineStr">
         <is>
           <t>순서</t>
         </is>
       </c>
-      <c r="B3" s="16" t="inlineStr">
+      <c r="B3" s="20" t="inlineStr">
         <is>
           <t>형상</t>
         </is>
       </c>
-      <c r="C3" s="16" t="inlineStr">
+      <c r="C3" s="20" t="inlineStr">
         <is>
           <t>날수(F)</t>
         </is>
       </c>
-      <c r="D3" s="16" t="inlineStr">
+      <c r="D3" s="20" t="inlineStr">
         <is>
           <t>날경(Ø)</t>
         </is>
       </c>
-      <c r="E3" s="16" t="inlineStr">
+      <c r="E3" s="20" t="inlineStr">
         <is>
           <t>상크경(Ø)</t>
         </is>
       </c>
-      <c r="F3" s="16" t="inlineStr">
+      <c r="F3" s="20" t="inlineStr">
         <is>
           <t>코팅</t>
         </is>
       </c>
-      <c r="G3" s="16" t="inlineStr">
+      <c r="G3" s="20" t="inlineStr">
         <is>
           <t>특이사항</t>
         </is>
       </c>
-      <c r="H3" s="16" t="inlineStr">
+      <c r="H3" s="20" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
       </c>
-      <c r="I3" s="16" t="inlineStr">
+      <c r="I3" s="20" t="inlineStr">
         <is>
           <t>수량(개)</t>
         </is>
       </c>
-      <c r="J3" s="16" t="inlineStr">
+      <c r="J3" s="20" t="inlineStr">
         <is>
           <t>시간합계(초)</t>
         </is>
       </c>
-      <c r="K3" s="16" t="inlineStr">
+      <c r="K3" s="20" t="inlineStr">
         <is>
           <t>시간(H:M:S)</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="17" t="inlineStr">
-        <is>
-          <t>(해당일 작업 없음)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="18" t="inlineStr">
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" s="22" t="inlineStr">
+        <is>
+          <t>면취</t>
+        </is>
+      </c>
+      <c r="C4" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="D4" s="21" t="n">
+        <v>6</v>
+      </c>
+      <c r="E4" s="21" t="n">
+        <v>6</v>
+      </c>
+      <c r="F4" s="22" t="inlineStr">
+        <is>
+          <t>뮤</t>
+        </is>
+      </c>
+      <c r="G4" s="22" t="inlineStr">
+        <is>
+          <t>0113 ㅋㅌ</t>
+        </is>
+      </c>
+      <c r="H4" s="21" t="inlineStr"/>
+      <c r="I4" s="23" t="n">
+        <v>9</v>
+      </c>
+      <c r="J4" s="23" t="n">
+        <v>2565</v>
+      </c>
+      <c r="K4" s="21" t="inlineStr">
+        <is>
+          <t>0:42:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="18" customHeight="1">
+      <c r="A5" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="B5" s="22" t="inlineStr">
+        <is>
+          <t>면취 60도</t>
+        </is>
+      </c>
+      <c r="C5" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="D5" s="21" t="n">
+        <v>6</v>
+      </c>
+      <c r="E5" s="21" t="n">
+        <v>6</v>
+      </c>
+      <c r="F5" s="22" t="inlineStr">
+        <is>
+          <t>비</t>
+        </is>
+      </c>
+      <c r="G5" s="22" t="inlineStr">
+        <is>
+          <t>0024</t>
+        </is>
+      </c>
+      <c r="H5" s="21" t="inlineStr"/>
+      <c r="I5" s="23" t="n">
+        <v>6</v>
+      </c>
+      <c r="J5" s="23" t="n">
+        <v>3600</v>
+      </c>
+      <c r="K5" s="21" t="inlineStr">
+        <is>
+          <t>1:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="18" customHeight="1">
+      <c r="A6" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="B6" s="22" t="inlineStr">
+        <is>
+          <t>면취</t>
+        </is>
+      </c>
+      <c r="C6" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="D6" s="21" t="n">
+        <v>6</v>
+      </c>
+      <c r="E6" s="21" t="n">
+        <v>6</v>
+      </c>
+      <c r="F6" s="22" t="inlineStr">
+        <is>
+          <t>비</t>
+        </is>
+      </c>
+      <c r="G6" s="22" t="inlineStr">
+        <is>
+          <t>0088</t>
+        </is>
+      </c>
+      <c r="H6" s="21" t="inlineStr"/>
+      <c r="I6" s="23" t="n">
+        <v>12</v>
+      </c>
+      <c r="J6" s="23" t="n">
+        <v>3420</v>
+      </c>
+      <c r="K6" s="21" t="inlineStr">
+        <is>
+          <t>0:57:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="17" t="inlineStr">
+        <is>
+          <t>FAST GRIND 소계</t>
+        </is>
+      </c>
+      <c r="B7" s="17" t="n"/>
+      <c r="C7" s="17" t="n"/>
+      <c r="D7" s="17" t="n"/>
+      <c r="E7" s="17" t="n"/>
+      <c r="F7" s="17" t="n"/>
+      <c r="G7" s="17" t="n"/>
+      <c r="H7" s="17" t="n"/>
+      <c r="I7" s="18" t="n">
+        <v>27</v>
+      </c>
+      <c r="J7" s="18" t="n">
+        <v>9585</v>
+      </c>
+      <c r="K7" s="17" t="inlineStr">
+        <is>
+          <t>2:39:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="22" customHeight="1">
+      <c r="A9" s="24" t="inlineStr">
         <is>
           <t>■ GX7</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
+    <row r="10" ht="20" customHeight="1">
+      <c r="A10" s="25" t="inlineStr">
         <is>
           <t>순서</t>
         </is>
       </c>
-      <c r="B7" s="19" t="inlineStr">
+      <c r="B10" s="25" t="inlineStr">
         <is>
           <t>형상</t>
         </is>
       </c>
-      <c r="C7" s="19" t="inlineStr">
+      <c r="C10" s="25" t="inlineStr">
         <is>
           <t>날수(F)</t>
         </is>
       </c>
-      <c r="D7" s="19" t="inlineStr">
+      <c r="D10" s="25" t="inlineStr">
         <is>
           <t>날경(Ø)</t>
         </is>
       </c>
-      <c r="E7" s="19" t="inlineStr">
+      <c r="E10" s="25" t="inlineStr">
         <is>
           <t>상크경(Ø)</t>
         </is>
       </c>
-      <c r="F7" s="19" t="inlineStr">
+      <c r="F10" s="25" t="inlineStr">
         <is>
           <t>코팅</t>
         </is>
       </c>
-      <c r="G7" s="19" t="inlineStr">
+      <c r="G10" s="25" t="inlineStr">
         <is>
           <t>특이사항</t>
         </is>
       </c>
-      <c r="H7" s="19" t="inlineStr">
+      <c r="H10" s="25" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
       </c>
-      <c r="I7" s="19" t="inlineStr">
+      <c r="I10" s="25" t="inlineStr">
         <is>
           <t>수량(개)</t>
         </is>
       </c>
-      <c r="J7" s="19" t="inlineStr">
+      <c r="J10" s="25" t="inlineStr">
         <is>
           <t>시간합계(초)</t>
         </is>
       </c>
-      <c r="K7" s="19" t="inlineStr">
+      <c r="K10" s="25" t="inlineStr">
         <is>
           <t>시간(H:M:S)</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="17" t="inlineStr">
-        <is>
-          <t>(해당일 작업 없음)</t>
+    <row r="11" ht="18" customHeight="1">
+      <c r="A11" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="B11" s="27" t="inlineStr">
+        <is>
+          <t>평</t>
+        </is>
+      </c>
+      <c r="C11" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="D11" s="26" t="n">
+        <v>10</v>
+      </c>
+      <c r="E11" s="26" t="n">
+        <v>10</v>
+      </c>
+      <c r="F11" s="27" t="inlineStr">
+        <is>
+          <t>뮤</t>
+        </is>
+      </c>
+      <c r="G11" s="27" t="inlineStr">
+        <is>
+          <t>0201, 0115 ㅋㅌ</t>
+        </is>
+      </c>
+      <c r="H11" s="26" t="inlineStr"/>
+      <c r="I11" s="28" t="n">
+        <v>10</v>
+      </c>
+      <c r="J11" s="28" t="n">
+        <v>1780</v>
+      </c>
+      <c r="K11" s="26" t="inlineStr">
+        <is>
+          <t>0:29:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="18" customHeight="1">
+      <c r="A12" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="B12" s="27" t="inlineStr">
+        <is>
+          <t>볼</t>
+        </is>
+      </c>
+      <c r="C12" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="D12" s="26" t="n">
+        <v>20</v>
+      </c>
+      <c r="E12" s="26" t="n">
+        <v>20</v>
+      </c>
+      <c r="F12" s="27" t="inlineStr">
+        <is>
+          <t>비</t>
+        </is>
+      </c>
+      <c r="G12" s="27" t="inlineStr">
+        <is>
+          <t>0052</t>
+        </is>
+      </c>
+      <c r="H12" s="26" t="inlineStr"/>
+      <c r="I12" s="28" t="n">
+        <v>4</v>
+      </c>
+      <c r="J12" s="28" t="n">
+        <v>4408</v>
+      </c>
+      <c r="K12" s="26" t="inlineStr">
+        <is>
+          <t>1:13:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="17" t="inlineStr">
+        <is>
+          <t>GX7 소계</t>
+        </is>
+      </c>
+      <c r="B13" s="17" t="n"/>
+      <c r="C13" s="17" t="n"/>
+      <c r="D13" s="17" t="n"/>
+      <c r="E13" s="17" t="n"/>
+      <c r="F13" s="17" t="n"/>
+      <c r="G13" s="17" t="n"/>
+      <c r="H13" s="17" t="n"/>
+      <c r="I13" s="18" t="n">
+        <v>14</v>
+      </c>
+      <c r="J13" s="18" t="n">
+        <v>6188</v>
+      </c>
+      <c r="K13" s="17" t="inlineStr">
+        <is>
+          <t>1:43:08</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="5">
-    <mergeCell ref="A6:K6"/>
-    <mergeCell ref="A4:K4"/>
+    <mergeCell ref="A7:H7"/>
     <mergeCell ref="A2:K2"/>
+    <mergeCell ref="A13:H13"/>
     <mergeCell ref="A1:K1"/>
-    <mergeCell ref="A8:K8"/>
+    <mergeCell ref="A9:K9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
